--- a/PTBR/Lang/PTBR/Dialog/Drama/guild_master_mage.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/guild_master_mage.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ah, mais um novato chega ao ninho. Pode botar ovos de ouro para mim, sim? Não desperdice meu tempo.  </t>
+          <t>Ah, mais um filhote novato no ninho. Pode botar ovos de ouro para mim, hein? Não desperdice o meu tempo.</t>
         </is>
       </c>
     </row>
